--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -987,7 +987,7 @@
         <v>4973</v>
       </c>
       <c r="J13" t="n">
-        <v>40917</v>
+        <v>41074</v>
       </c>
       <c r="K13" t="n">
         <v>12140</v>
@@ -996,7 +996,7 @@
         <v>291915</v>
       </c>
       <c r="M13" t="n">
-        <v>519595</v>
+        <v>519752</v>
       </c>
     </row>
     <row r="14">
@@ -1006,40 +1006,40 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>637</v>
+        <v>661</v>
       </c>
       <c r="C14" t="n">
-        <v>667</v>
+        <v>700</v>
       </c>
       <c r="D14" t="n">
-        <v>48.8</v>
+        <v>48.6</v>
       </c>
       <c r="E14" t="n">
-        <v>840</v>
+        <v>870</v>
       </c>
       <c r="F14" t="n">
-        <v>1029</v>
+        <v>1097</v>
       </c>
       <c r="G14" t="n">
-        <v>974</v>
+        <v>1005</v>
       </c>
       <c r="H14" t="n">
-        <v>1213</v>
+        <v>1287</v>
       </c>
       <c r="I14" t="n">
-        <v>1403</v>
+        <v>1632</v>
       </c>
       <c r="J14" t="n">
-        <v>40288</v>
+        <v>43396</v>
       </c>
       <c r="K14" t="n">
-        <v>12777</v>
+        <v>12801</v>
       </c>
       <c r="L14" t="n">
-        <v>293318</v>
+        <v>293547</v>
       </c>
       <c r="M14" t="n">
-        <v>559883</v>
+        <v>563148</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1009,7 +1009,7 @@
         <v>661</v>
       </c>
       <c r="C14" t="n">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D14" t="n">
         <v>48.6</v>
@@ -1018,13 +1018,13 @@
         <v>870</v>
       </c>
       <c r="F14" t="n">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="G14" t="n">
         <v>1005</v>
       </c>
       <c r="H14" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="I14" t="n">
         <v>1632</v>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1006,25 +1006,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>661</v>
+        <v>693</v>
       </c>
       <c r="C14" t="n">
-        <v>699</v>
+        <v>721</v>
       </c>
       <c r="D14" t="n">
-        <v>48.6</v>
+        <v>49</v>
       </c>
       <c r="E14" t="n">
-        <v>870</v>
+        <v>914</v>
       </c>
       <c r="F14" t="n">
-        <v>1096</v>
+        <v>1142</v>
       </c>
       <c r="G14" t="n">
-        <v>1005</v>
+        <v>1053</v>
       </c>
       <c r="H14" t="n">
-        <v>1286</v>
+        <v>1334</v>
       </c>
       <c r="I14" t="n">
         <v>1632</v>
@@ -1033,7 +1033,7 @@
         <v>43396</v>
       </c>
       <c r="K14" t="n">
-        <v>12801</v>
+        <v>12833</v>
       </c>
       <c r="L14" t="n">
         <v>293547</v>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -984,19 +984,19 @@
         <v>598</v>
       </c>
       <c r="I13" t="n">
-        <v>4973</v>
+        <v>4997</v>
       </c>
       <c r="J13" t="n">
-        <v>41074</v>
+        <v>41179</v>
       </c>
       <c r="K13" t="n">
         <v>12140</v>
       </c>
       <c r="L13" t="n">
-        <v>291915</v>
+        <v>291939</v>
       </c>
       <c r="M13" t="n">
-        <v>519752</v>
+        <v>519857</v>
       </c>
     </row>
     <row r="14">
@@ -1006,40 +1006,40 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="C14" t="n">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="D14" t="n">
         <v>49</v>
       </c>
       <c r="E14" t="n">
-        <v>914</v>
+        <v>919</v>
       </c>
       <c r="F14" t="n">
-        <v>1142</v>
+        <v>1147</v>
       </c>
       <c r="G14" t="n">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="H14" t="n">
-        <v>1334</v>
+        <v>1339</v>
       </c>
       <c r="I14" t="n">
-        <v>1632</v>
+        <v>2048</v>
       </c>
       <c r="J14" t="n">
-        <v>43396</v>
+        <v>46401</v>
       </c>
       <c r="K14" t="n">
-        <v>12833</v>
+        <v>12836</v>
       </c>
       <c r="L14" t="n">
-        <v>293547</v>
+        <v>293987</v>
       </c>
       <c r="M14" t="n">
-        <v>563148</v>
+        <v>566258</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -984,19 +984,19 @@
         <v>598</v>
       </c>
       <c r="I13" t="n">
-        <v>4997</v>
+        <v>5007</v>
       </c>
       <c r="J13" t="n">
-        <v>41179</v>
+        <v>41244</v>
       </c>
       <c r="K13" t="n">
         <v>12140</v>
       </c>
       <c r="L13" t="n">
-        <v>291939</v>
+        <v>291949</v>
       </c>
       <c r="M13" t="n">
-        <v>519857</v>
+        <v>519922</v>
       </c>
     </row>
     <row r="14">
@@ -1006,40 +1006,40 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>696</v>
+        <v>711</v>
       </c>
       <c r="C14" t="n">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="D14" t="n">
-        <v>49</v>
+        <v>49.4</v>
       </c>
       <c r="E14" t="n">
-        <v>919</v>
+        <v>938</v>
       </c>
       <c r="F14" t="n">
-        <v>1147</v>
+        <v>1155</v>
       </c>
       <c r="G14" t="n">
-        <v>1059</v>
+        <v>1078</v>
       </c>
       <c r="H14" t="n">
-        <v>1339</v>
+        <v>1348</v>
       </c>
       <c r="I14" t="n">
-        <v>2048</v>
+        <v>2339</v>
       </c>
       <c r="J14" t="n">
-        <v>46401</v>
+        <v>48999</v>
       </c>
       <c r="K14" t="n">
-        <v>12836</v>
+        <v>12851</v>
       </c>
       <c r="L14" t="n">
-        <v>293987</v>
+        <v>294288</v>
       </c>
       <c r="M14" t="n">
-        <v>566258</v>
+        <v>568921</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -941,19 +941,19 @@
         <v>656</v>
       </c>
       <c r="I12" t="n">
-        <v>18659</v>
+        <v>18589</v>
       </c>
       <c r="J12" t="n">
-        <v>130765</v>
+        <v>130742</v>
       </c>
       <c r="K12" t="n">
         <v>9759</v>
       </c>
       <c r="L12" t="n">
-        <v>286942</v>
+        <v>286872</v>
       </c>
       <c r="M12" t="n">
-        <v>478678</v>
+        <v>478655</v>
       </c>
     </row>
     <row r="13">
@@ -984,19 +984,19 @@
         <v>598</v>
       </c>
       <c r="I13" t="n">
-        <v>5007</v>
+        <v>5046</v>
       </c>
       <c r="J13" t="n">
-        <v>41244</v>
+        <v>41788</v>
       </c>
       <c r="K13" t="n">
         <v>12140</v>
       </c>
       <c r="L13" t="n">
-        <v>291949</v>
+        <v>291918</v>
       </c>
       <c r="M13" t="n">
-        <v>519922</v>
+        <v>520443</v>
       </c>
     </row>
     <row r="14">
@@ -1006,40 +1006,40 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>711</v>
+        <v>741</v>
       </c>
       <c r="C14" t="n">
-        <v>727</v>
+        <v>743</v>
       </c>
       <c r="D14" t="n">
-        <v>49.4</v>
+        <v>49.9</v>
       </c>
       <c r="E14" t="n">
-        <v>938</v>
+        <v>981</v>
       </c>
       <c r="F14" t="n">
-        <v>1155</v>
+        <v>1197</v>
       </c>
       <c r="G14" t="n">
-        <v>1078</v>
+        <v>1128</v>
       </c>
       <c r="H14" t="n">
-        <v>1348</v>
+        <v>1393</v>
       </c>
       <c r="I14" t="n">
-        <v>2339</v>
+        <v>3550</v>
       </c>
       <c r="J14" t="n">
-        <v>48999</v>
+        <v>57863</v>
       </c>
       <c r="K14" t="n">
-        <v>12851</v>
+        <v>12881</v>
       </c>
       <c r="L14" t="n">
-        <v>294288</v>
+        <v>295468</v>
       </c>
       <c r="M14" t="n">
-        <v>568921</v>
+        <v>578306</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1006,25 +1006,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="C14" t="n">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D14" t="n">
-        <v>49.9</v>
+        <v>50.1</v>
       </c>
       <c r="E14" t="n">
-        <v>981</v>
+        <v>989</v>
       </c>
       <c r="F14" t="n">
-        <v>1197</v>
+        <v>1202</v>
       </c>
       <c r="G14" t="n">
-        <v>1128</v>
+        <v>1136</v>
       </c>
       <c r="H14" t="n">
-        <v>1393</v>
+        <v>1399</v>
       </c>
       <c r="I14" t="n">
         <v>3550</v>
@@ -1033,7 +1033,7 @@
         <v>57863</v>
       </c>
       <c r="K14" t="n">
-        <v>12881</v>
+        <v>12888</v>
       </c>
       <c r="L14" t="n">
         <v>295468</v>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -984,19 +984,19 @@
         <v>598</v>
       </c>
       <c r="I13" t="n">
-        <v>5046</v>
+        <v>5056</v>
       </c>
       <c r="J13" t="n">
-        <v>41788</v>
+        <v>41886</v>
       </c>
       <c r="K13" t="n">
         <v>12140</v>
       </c>
       <c r="L13" t="n">
-        <v>291918</v>
+        <v>291928</v>
       </c>
       <c r="M13" t="n">
-        <v>520443</v>
+        <v>520541</v>
       </c>
     </row>
     <row r="14">
@@ -1027,19 +1027,19 @@
         <v>1399</v>
       </c>
       <c r="I14" t="n">
-        <v>3550</v>
+        <v>4016</v>
       </c>
       <c r="J14" t="n">
-        <v>57863</v>
+        <v>61564</v>
       </c>
       <c r="K14" t="n">
         <v>12888</v>
       </c>
       <c r="L14" t="n">
-        <v>295468</v>
+        <v>295944</v>
       </c>
       <c r="M14" t="n">
-        <v>578306</v>
+        <v>582105</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1006,25 +1006,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>748</v>
+        <v>818</v>
       </c>
       <c r="C14" t="n">
-        <v>744</v>
+        <v>765</v>
       </c>
       <c r="D14" t="n">
-        <v>50.1</v>
+        <v>51.7</v>
       </c>
       <c r="E14" t="n">
-        <v>989</v>
+        <v>1085</v>
       </c>
       <c r="F14" t="n">
-        <v>1202</v>
+        <v>1239</v>
       </c>
       <c r="G14" t="n">
-        <v>1136</v>
+        <v>1236</v>
       </c>
       <c r="H14" t="n">
-        <v>1399</v>
+        <v>1440</v>
       </c>
       <c r="I14" t="n">
         <v>4016</v>
@@ -1033,7 +1033,7 @@
         <v>61564</v>
       </c>
       <c r="K14" t="n">
-        <v>12888</v>
+        <v>12958</v>
       </c>
       <c r="L14" t="n">
         <v>295944</v>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1006,25 +1006,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>818</v>
+        <v>828</v>
       </c>
       <c r="C14" t="n">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="D14" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
       <c r="E14" t="n">
-        <v>1085</v>
+        <v>1096</v>
       </c>
       <c r="F14" t="n">
-        <v>1239</v>
+        <v>1254</v>
       </c>
       <c r="G14" t="n">
-        <v>1236</v>
+        <v>1247</v>
       </c>
       <c r="H14" t="n">
-        <v>1440</v>
+        <v>1461</v>
       </c>
       <c r="I14" t="n">
         <v>4016</v>
@@ -1033,7 +1033,7 @@
         <v>61564</v>
       </c>
       <c r="K14" t="n">
-        <v>12958</v>
+        <v>12968</v>
       </c>
       <c r="L14" t="n">
         <v>295944</v>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -984,19 +984,19 @@
         <v>598</v>
       </c>
       <c r="I13" t="n">
-        <v>5056</v>
+        <v>5370</v>
       </c>
       <c r="J13" t="n">
-        <v>41886</v>
+        <v>42174</v>
       </c>
       <c r="K13" t="n">
         <v>12140</v>
       </c>
       <c r="L13" t="n">
-        <v>291928</v>
+        <v>292242</v>
       </c>
       <c r="M13" t="n">
-        <v>520541</v>
+        <v>520829</v>
       </c>
     </row>
     <row r="14">
@@ -1027,19 +1027,19 @@
         <v>1461</v>
       </c>
       <c r="I14" t="n">
-        <v>4016</v>
+        <v>6602</v>
       </c>
       <c r="J14" t="n">
-        <v>61564</v>
+        <v>83028</v>
       </c>
       <c r="K14" t="n">
         <v>12968</v>
       </c>
       <c r="L14" t="n">
-        <v>295944</v>
+        <v>298844</v>
       </c>
       <c r="M14" t="n">
-        <v>582105</v>
+        <v>603857</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1006,25 +1006,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C14" t="n">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D14" t="n">
         <v>51.8</v>
       </c>
       <c r="E14" t="n">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="F14" t="n">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="G14" t="n">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="H14" t="n">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="I14" t="n">
         <v>6602</v>
@@ -1033,7 +1033,7 @@
         <v>83028</v>
       </c>
       <c r="K14" t="n">
-        <v>12968</v>
+        <v>12969</v>
       </c>
       <c r="L14" t="n">
         <v>298844</v>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -877,25 +877,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="C11" t="n">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="D11" t="n">
-        <v>61.5</v>
+        <v>60.9</v>
       </c>
       <c r="E11" t="n">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="F11" t="n">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="G11" t="n">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="H11" t="n">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="I11" t="n">
         <v>12435</v>
@@ -904,7 +904,7 @@
         <v>49788</v>
       </c>
       <c r="K11" t="n">
-        <v>6715</v>
+        <v>6708</v>
       </c>
       <c r="L11" t="n">
         <v>268283</v>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3044</v>
+        <v>3041</v>
       </c>
       <c r="C12" t="n">
         <v>511</v>
@@ -929,31 +929,31 @@
         <v>85.59999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>3169</v>
+        <v>3168</v>
       </c>
       <c r="F12" t="n">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="G12" t="n">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="H12" t="n">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="I12" t="n">
         <v>18589</v>
       </c>
       <c r="J12" t="n">
-        <v>130742</v>
+        <v>130908</v>
       </c>
       <c r="K12" t="n">
-        <v>9759</v>
+        <v>9749</v>
       </c>
       <c r="L12" t="n">
         <v>286872</v>
       </c>
       <c r="M12" t="n">
-        <v>478655</v>
+        <v>478821</v>
       </c>
     </row>
     <row r="13">
@@ -963,40 +963,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2381</v>
+        <v>2382</v>
       </c>
       <c r="C13" t="n">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="D13" t="n">
-        <v>85.09999999999999</v>
+        <v>85</v>
       </c>
       <c r="E13" t="n">
         <v>2467</v>
       </c>
       <c r="F13" t="n">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="G13" t="n">
-        <v>2484</v>
+        <v>2483</v>
       </c>
       <c r="H13" t="n">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="I13" t="n">
-        <v>5370</v>
+        <v>5436</v>
       </c>
       <c r="J13" t="n">
-        <v>42174</v>
+        <v>42184</v>
       </c>
       <c r="K13" t="n">
-        <v>12140</v>
+        <v>12131</v>
       </c>
       <c r="L13" t="n">
-        <v>292242</v>
+        <v>292308</v>
       </c>
       <c r="M13" t="n">
-        <v>520829</v>
+        <v>521005</v>
       </c>
     </row>
     <row r="14">
@@ -1006,40 +1006,40 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>829</v>
+        <v>871</v>
       </c>
       <c r="C14" t="n">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="D14" t="n">
-        <v>51.8</v>
+        <v>52.9</v>
       </c>
       <c r="E14" t="n">
-        <v>1097</v>
+        <v>1151</v>
       </c>
       <c r="F14" t="n">
-        <v>1255</v>
+        <v>1264</v>
       </c>
       <c r="G14" t="n">
-        <v>1248</v>
+        <v>1309</v>
       </c>
       <c r="H14" t="n">
-        <v>1462</v>
+        <v>1470</v>
       </c>
       <c r="I14" t="n">
-        <v>6602</v>
+        <v>7494</v>
       </c>
       <c r="J14" t="n">
-        <v>83028</v>
+        <v>85971</v>
       </c>
       <c r="K14" t="n">
-        <v>12969</v>
+        <v>13002</v>
       </c>
       <c r="L14" t="n">
-        <v>298844</v>
+        <v>299802</v>
       </c>
       <c r="M14" t="n">
-        <v>603857</v>
+        <v>606976</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1092,25 +1092,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="D16" t="n">
-        <v>61.4</v>
+        <v>58.7</v>
       </c>
       <c r="E16" t="n">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="F16" t="n">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="G16" t="n">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="H16" t="n">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1119,7 +1119,7 @@
         <v>3853</v>
       </c>
       <c r="K16" t="n">
-        <v>13110</v>
+        <v>13126</v>
       </c>
       <c r="L16" t="n">
         <v>301200</v>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1030,7 +1030,7 @@
         <v>5362</v>
       </c>
       <c r="J14" t="n">
-        <v>40436</v>
+        <v>40795</v>
       </c>
       <c r="K14" t="n">
         <v>12147</v>
@@ -1039,7 +1039,7 @@
         <v>293650</v>
       </c>
       <c r="M14" t="n">
-        <v>525294</v>
+        <v>525653</v>
       </c>
     </row>
     <row r="15">
@@ -1070,19 +1070,19 @@
         <v>1511</v>
       </c>
       <c r="I15" t="n">
-        <v>7550</v>
+        <v>8241</v>
       </c>
       <c r="J15" t="n">
-        <v>92706</v>
+        <v>97058</v>
       </c>
       <c r="K15" t="n">
         <v>12994</v>
       </c>
       <c r="L15" t="n">
-        <v>301200</v>
+        <v>301891</v>
       </c>
       <c r="M15" t="n">
-        <v>618000</v>
+        <v>622711</v>
       </c>
     </row>
     <row r="16">
@@ -1113,19 +1113,19 @@
         <v>107</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="J16" t="n">
-        <v>3853</v>
+        <v>9496</v>
       </c>
       <c r="K16" t="n">
         <v>13126</v>
       </c>
       <c r="L16" t="n">
-        <v>301200</v>
+        <v>302000</v>
       </c>
       <c r="M16" t="n">
-        <v>621853</v>
+        <v>632207</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1095,28 +1095,28 @@
         <v>132</v>
       </c>
       <c r="C16" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D16" t="n">
-        <v>58.7</v>
+        <v>58.9</v>
       </c>
       <c r="E16" t="n">
         <v>139</v>
       </c>
       <c r="F16" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G16" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H16" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I16" t="n">
         <v>109</v>
       </c>
       <c r="J16" t="n">
-        <v>9496</v>
+        <v>9561</v>
       </c>
       <c r="K16" t="n">
         <v>13126</v>
@@ -1125,7 +1125,7 @@
         <v>302000</v>
       </c>
       <c r="M16" t="n">
-        <v>632207</v>
+        <v>632272</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1009,28 +1009,28 @@
         <v>2368</v>
       </c>
       <c r="C14" t="n">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D14" t="n">
-        <v>84.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="E14" t="n">
         <v>2453</v>
       </c>
       <c r="F14" t="n">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="G14" t="n">
         <v>2469</v>
       </c>
       <c r="H14" t="n">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="I14" t="n">
         <v>5362</v>
       </c>
       <c r="J14" t="n">
-        <v>40795</v>
+        <v>40915</v>
       </c>
       <c r="K14" t="n">
         <v>12147</v>
@@ -1039,7 +1039,7 @@
         <v>293650</v>
       </c>
       <c r="M14" t="n">
-        <v>525653</v>
+        <v>525773</v>
       </c>
     </row>
     <row r="15">
@@ -1070,19 +1070,19 @@
         <v>1511</v>
       </c>
       <c r="I15" t="n">
-        <v>8241</v>
+        <v>8318</v>
       </c>
       <c r="J15" t="n">
-        <v>97058</v>
+        <v>98313</v>
       </c>
       <c r="K15" t="n">
         <v>12994</v>
       </c>
       <c r="L15" t="n">
-        <v>301891</v>
+        <v>301968</v>
       </c>
       <c r="M15" t="n">
-        <v>622711</v>
+        <v>624086</v>
       </c>
     </row>
     <row r="16">
@@ -1092,40 +1092,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C16" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D16" t="n">
-        <v>58.9</v>
+        <v>58.6</v>
       </c>
       <c r="E16" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="F16" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="H16" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I16" t="n">
-        <v>109</v>
+        <v>197</v>
       </c>
       <c r="J16" t="n">
-        <v>9561</v>
+        <v>11733</v>
       </c>
       <c r="K16" t="n">
-        <v>13126</v>
+        <v>13130</v>
       </c>
       <c r="L16" t="n">
-        <v>302000</v>
+        <v>302165</v>
       </c>
       <c r="M16" t="n">
-        <v>632272</v>
+        <v>635819</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1,40 +1,135 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>New_creators</t>
+  </si>
+  <si>
+    <t>Old_creators</t>
+  </si>
+  <si>
+    <t>New_share_pct</t>
+  </si>
+  <si>
+    <t>Sample_orders_new</t>
+  </si>
+  <si>
+    <t>Sample_orders_old</t>
+  </si>
+  <si>
+    <t>Sample_units_new</t>
+  </si>
+  <si>
+    <t>Sample_units_old</t>
+  </si>
+  <si>
+    <t>Video_GMV_new</t>
+  </si>
+  <si>
+    <t>Video_GMV_old</t>
+  </si>
+  <si>
+    <t>Cum_new_creators</t>
+  </si>
+  <si>
+    <t>Cum_GMV_new</t>
+  </si>
+  <si>
+    <t>Cum_GMV_old</t>
+  </si>
+  <si>
+    <t>2025-07</t>
+  </si>
+  <si>
+    <t>2025-08</t>
+  </si>
+  <si>
+    <t>2025-09</t>
+  </si>
+  <si>
+    <t>2025-10</t>
+  </si>
+  <si>
+    <t>2025-11</t>
+  </si>
+  <si>
+    <t>2025-12</t>
+  </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>2026-03</t>
+  </si>
+  <si>
+    <t>2026-04</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +137,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,727 +454,667 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>New_creators</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Old_creators</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>New_share_pct</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Sample_orders_new</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Sample_orders_old</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Sample_units_new</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Sample_units_old</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Video_GMV_new</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Video_GMV_old</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Cum_new_creators</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Cum_GMV_new</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Cum_GMV_old</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
         <v>70</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
         <v>100</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>70</v>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
         <v>70</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
         <v>2730</v>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
         <v>70</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>2730</v>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
         <v>41</v>
       </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
         <v>100</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>41</v>
       </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
         <v>41</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
         <v>6899</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>10092</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>111</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>9629</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>10092</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
         <v>432</v>
       </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
         <v>100</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>432</v>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
         <v>433</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
         <v>62850</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>11972</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>543</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>72479</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>22064</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
         <v>568</v>
       </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
         <v>100</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>568</v>
       </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>568</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
         <v>6258</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>56244</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>1111</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>78737</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>78308</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:13">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
         <v>629</v>
       </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
         <v>100</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>629</v>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
         <v>629</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
         <v>11071</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>49346</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>1740</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>89808</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>127654</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:13">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
         <v>431</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>1</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>99.8</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>431</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>1</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>431</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>1</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>2171</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>37862</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>2171</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>91979</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>165516</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:13">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
         <v>811</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>8</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>99</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>818</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>8</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>891</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>15</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>11103</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>10409</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>2982</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>103082</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>175925</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:13">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9">
         <v>821</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>19</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>97.7</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>856</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>21</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>1033</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>28</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>12312</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>32847</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>3803</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>115394</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>208772</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:13">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10">
         <v>1486</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>28</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>98.2</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>1501</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>31</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>1580</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>32</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>73914</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>62642</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>5289</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>189308</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>271414</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:13">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11">
         <v>877</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>93</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>90.40000000000001</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>890</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>99</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>894</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>105</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>68334</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>35898</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>6166</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>257642</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>307312</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:13">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12">
         <v>587</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>392</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>60</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>689</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>447</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>699</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>451</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>12385</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>49429</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>6753</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>270027</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>356741</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="13" spans="1:13">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13">
         <v>3026</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>512</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>85.5</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>3153</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>644</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>3184</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>658</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>18261</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>128117</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>9779</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>288288</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13">
         <v>484858</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+    <row r="14" spans="1:13">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14">
         <v>2368</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>421</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>84.90000000000001</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>2453</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>569</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>2469</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>604</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>5362</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>40915</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14">
         <v>12147</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14">
         <v>293650</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14">
         <v>525773</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="15" spans="1:13">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15">
         <v>847</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>797</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>51.5</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>1117</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>1298</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>1268</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>1511</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>8318</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>98313</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>12994</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15">
         <v>301968</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15">
         <v>624086</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+    <row r="16" spans="1:13">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16">
         <v>136</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>96</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>58.6</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>145</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>100</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>170</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>110</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>197</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16">
         <v>11733</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>13130</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16">
         <v>302165</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16">
         <v>635819</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1092,25 +1092,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="C16" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="D16" t="n">
-        <v>54.2</v>
+        <v>54.5</v>
       </c>
       <c r="E16" t="n">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="F16" t="n">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="G16" t="n">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="H16" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="I16" t="n">
         <v>197</v>
@@ -1119,7 +1119,7 @@
         <v>11733</v>
       </c>
       <c r="K16" t="n">
-        <v>13144</v>
+        <v>13157</v>
       </c>
       <c r="L16" t="n">
         <v>302165</v>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1030,7 +1030,7 @@
         <v>5362</v>
       </c>
       <c r="J14" t="n">
-        <v>40915</v>
+        <v>40997</v>
       </c>
       <c r="K14" t="n">
         <v>12147</v>
@@ -1039,7 +1039,7 @@
         <v>293650</v>
       </c>
       <c r="M14" t="n">
-        <v>525773</v>
+        <v>525855</v>
       </c>
     </row>
     <row r="15">
@@ -1070,19 +1070,19 @@
         <v>1511</v>
       </c>
       <c r="I15" t="n">
-        <v>8318</v>
+        <v>8543</v>
       </c>
       <c r="J15" t="n">
-        <v>98313</v>
+        <v>100188</v>
       </c>
       <c r="K15" t="n">
         <v>12994</v>
       </c>
       <c r="L15" t="n">
-        <v>301968</v>
+        <v>302193</v>
       </c>
       <c r="M15" t="n">
-        <v>624086</v>
+        <v>626043</v>
       </c>
     </row>
     <row r="16">
@@ -1113,19 +1113,19 @@
         <v>152</v>
       </c>
       <c r="I16" t="n">
-        <v>197</v>
+        <v>417</v>
       </c>
       <c r="J16" t="n">
-        <v>11733</v>
+        <v>13681</v>
       </c>
       <c r="K16" t="n">
         <v>13157</v>
       </c>
       <c r="L16" t="n">
-        <v>302165</v>
+        <v>302610</v>
       </c>
       <c r="M16" t="n">
-        <v>635819</v>
+        <v>639724</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1027,19 +1027,19 @@
         <v>604</v>
       </c>
       <c r="I14" t="n">
-        <v>5362</v>
+        <v>5439</v>
       </c>
       <c r="J14" t="n">
-        <v>40997</v>
+        <v>41078</v>
       </c>
       <c r="K14" t="n">
         <v>12147</v>
       </c>
       <c r="L14" t="n">
-        <v>293650</v>
+        <v>293727</v>
       </c>
       <c r="M14" t="n">
-        <v>525855</v>
+        <v>525936</v>
       </c>
     </row>
     <row r="15">
@@ -1070,19 +1070,19 @@
         <v>1511</v>
       </c>
       <c r="I15" t="n">
-        <v>8543</v>
+        <v>8684</v>
       </c>
       <c r="J15" t="n">
-        <v>100188</v>
+        <v>101691</v>
       </c>
       <c r="K15" t="n">
         <v>12994</v>
       </c>
       <c r="L15" t="n">
-        <v>302193</v>
+        <v>302411</v>
       </c>
       <c r="M15" t="n">
-        <v>626043</v>
+        <v>627627</v>
       </c>
     </row>
     <row r="16">
@@ -1092,40 +1092,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="C16" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D16" t="n">
-        <v>54.5</v>
+        <v>55.9</v>
       </c>
       <c r="E16" t="n">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="F16" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G16" t="n">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="H16" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I16" t="n">
-        <v>417</v>
+        <v>461</v>
       </c>
       <c r="J16" t="n">
-        <v>13681</v>
+        <v>16497</v>
       </c>
       <c r="K16" t="n">
-        <v>13157</v>
+        <v>13168</v>
       </c>
       <c r="L16" t="n">
-        <v>302610</v>
+        <v>302872</v>
       </c>
       <c r="M16" t="n">
-        <v>639724</v>
+        <v>644124</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1027,19 +1027,19 @@
         <v>604</v>
       </c>
       <c r="I14" t="n">
-        <v>5439</v>
+        <v>5491</v>
       </c>
       <c r="J14" t="n">
-        <v>41078</v>
+        <v>41110</v>
       </c>
       <c r="K14" t="n">
         <v>12147</v>
       </c>
       <c r="L14" t="n">
-        <v>293727</v>
+        <v>293779</v>
       </c>
       <c r="M14" t="n">
-        <v>525936</v>
+        <v>525968</v>
       </c>
     </row>
     <row r="15">
@@ -1070,19 +1070,19 @@
         <v>1511</v>
       </c>
       <c r="I15" t="n">
-        <v>8684</v>
+        <v>8743</v>
       </c>
       <c r="J15" t="n">
-        <v>101691</v>
+        <v>103332</v>
       </c>
       <c r="K15" t="n">
         <v>12994</v>
       </c>
       <c r="L15" t="n">
-        <v>302411</v>
+        <v>302522</v>
       </c>
       <c r="M15" t="n">
-        <v>627627</v>
+        <v>629300</v>
       </c>
     </row>
     <row r="16">
@@ -1113,19 +1113,19 @@
         <v>153</v>
       </c>
       <c r="I16" t="n">
-        <v>461</v>
+        <v>504</v>
       </c>
       <c r="J16" t="n">
-        <v>16497</v>
+        <v>18249</v>
       </c>
       <c r="K16" t="n">
         <v>13168</v>
       </c>
       <c r="L16" t="n">
-        <v>302872</v>
+        <v>303026</v>
       </c>
       <c r="M16" t="n">
-        <v>644124</v>
+        <v>647549</v>
       </c>
     </row>
   </sheetData>
